--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,11 +122,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +167,8 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2101,7 +2104,7 @@
           <t>Fixtures — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="30" t="n"/>
       <c r="D7" s="4" t="n">
         <v>750</v>
       </c>
@@ -2112,7 +2115,7 @@
           <t>Laptop — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n"/>
+      <c r="C8" s="30" t="n"/>
       <c r="D8" s="4" t="n">
         <v>610</v>
       </c>
@@ -2234,7 +2237,7 @@
           <t>Parts used — Priya S.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n"/>
+      <c r="C20" s="30" t="n"/>
       <c r="D20" s="4" t="n">
         <v>-25</v>
       </c>
@@ -3248,7 +3251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="B1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
@@ -2098,7 +2098,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="7" collapsed="1">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Fixtures — Company received at formation (June 1)</t>
@@ -2109,7 +2109,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Laptop — Company received at formation (June 1)</t>
@@ -2120,7 +2120,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Credit Card — Company assumed the claim at formation (June 1)</t>
@@ -2130,7 +2130,7 @@
         <v>-2030</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Customer Deposit — Company assumed the claim at formation (June 1)</t>
@@ -2141,7 +2141,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1">
+    <row r="11" collapsed="1">
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2154,7 +2154,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" hidden="1" outlineLevel="1">
+    <row r="12">
       <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2167,11 +2167,11 @@
         <v/>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1">
+    <row r="13">
       <c r="B13" s="3" t="n"/>
       <c r="D13" s="4" t="n"/>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
+    <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t>GENERATED</t>
@@ -2180,7 +2180,7 @@
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1">
+    <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2231,7 +2231,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" collapsed="1">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Parts used — Priya S.</t>
@@ -2242,7 +2242,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="21" outlineLevel="1">
+    <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Liam O.</t>
@@ -2252,7 +2252,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="22" outlineLevel="1">
+    <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Parts used — Liam O.</t>
@@ -2262,7 +2262,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="23" outlineLevel="1">
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Sofia M.</t>
@@ -2272,7 +2272,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" outlineLevel="1">
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Jamal W.</t>
@@ -2282,7 +2282,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="25" outlineLevel="1">
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Parts used — Jamal W.</t>
@@ -2292,7 +2292,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="26" outlineLevel="1">
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Erin K.</t>
@@ -2302,7 +2302,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Parts used — Erin K.</t>
@@ -2312,7 +2312,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="28" outlineLevel="1">
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Noah B.</t>
@@ -2322,7 +2322,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" outlineLevel="1">
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Parts used — Noah B.</t>
@@ -2332,7 +2332,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="30" outlineLevel="1">
+    <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Rent used — June</t>
@@ -2342,7 +2342,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="31" outlineLevel="1">
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Rent used — July</t>
@@ -2352,7 +2352,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="32" outlineLevel="1">
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Grace L.</t>
@@ -2362,7 +2362,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="33" outlineLevel="1">
+    <row r="33" hidden="1" outlineLevel="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Parts used — Grace L.</t>
@@ -2372,7 +2372,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="34" outlineLevel="1">
+    <row r="34" hidden="1" outlineLevel="1">
       <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Theo H.</t>
@@ -2382,7 +2382,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35" outlineLevel="1">
+    <row r="35" hidden="1" outlineLevel="1">
       <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Parts used — Theo H.</t>
@@ -2392,7 +2392,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="36" outlineLevel="1">
+    <row r="36" hidden="1" outlineLevel="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Maya P.</t>
@@ -2402,7 +2402,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" outlineLevel="1">
+    <row r="37" hidden="1" outlineLevel="1">
       <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Parts used — Maya P.</t>
@@ -2412,7 +2412,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="38" outlineLevel="1">
+    <row r="38" hidden="1" outlineLevel="1">
       <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Owen C.</t>
@@ -2422,7 +2422,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="39" outlineLevel="1">
+    <row r="39" hidden="1" outlineLevel="1">
       <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Parts used — Owen C.</t>
@@ -2432,7 +2432,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="40" outlineLevel="1">
+    <row r="40" hidden="1" outlineLevel="1">
       <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Ava D.</t>
@@ -2442,7 +2442,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" outlineLevel="1">
+    <row r="41" hidden="1" outlineLevel="1">
       <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ava D.</t>
@@ -2452,7 +2452,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="42" outlineLevel="1">
+    <row r="42" hidden="1" outlineLevel="1">
       <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Leo F.</t>
@@ -2462,7 +2462,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" outlineLevel="1">
+    <row r="43" hidden="1" outlineLevel="1">
       <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Parts used — Leo F.</t>
@@ -2472,7 +2472,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="44" outlineLevel="1">
+    <row r="44" hidden="1" outlineLevel="1">
       <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Nina V.</t>
@@ -2482,7 +2482,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="45" outlineLevel="1">
+    <row r="45" hidden="1" outlineLevel="1">
       <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Parts used — Nina V.</t>
@@ -2492,7 +2492,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="46" outlineLevel="1">
+    <row r="46" hidden="1" outlineLevel="1">
       <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Rent used — August</t>
@@ -2502,7 +2502,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="47" outlineLevel="1">
+    <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Caleb G.</t>
@@ -2512,7 +2512,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="48" outlineLevel="1">
+    <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Parts used — Caleb G.</t>
@@ -2522,7 +2522,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="49" outlineLevel="1">
+    <row r="49" hidden="1" outlineLevel="1">
       <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Ruth A.</t>
@@ -2532,7 +2532,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="50" outlineLevel="1">
+    <row r="50" hidden="1" outlineLevel="1">
       <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ruth A.</t>
@@ -2542,7 +2542,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="51" outlineLevel="1">
+    <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Sam Q.</t>
@@ -2552,7 +2552,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="52" outlineLevel="1">
+    <row r="52" hidden="1" outlineLevel="1">
       <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Parts used — Sam Q.</t>
@@ -2562,7 +2562,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="53" outlineLevel="1">
+    <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Repair collected — Westville Bike Share</t>
@@ -2572,7 +2572,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="54" outlineLevel="1">
+    <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Parts used — Westville Bike Share</t>
@@ -2582,7 +2582,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="55" outlineLevel="1">
+    <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Repair delivered — Ridgeline Trail Crew, billed net 15 (unpaid)</t>
@@ -2592,7 +2592,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="56" outlineLevel="1">
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="3" t="inlineStr">
         <is>
           <t>Parts used — Ridgeline Trail Crew</t>
@@ -2602,7 +2602,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
+    <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Frame delivered — J. Smith (deposit earned)</t>
@@ -2612,7 +2612,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" outlineLevel="1">
+    <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Parts used — J. Smith</t>
@@ -2622,7 +2622,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="59" outlineLevel="1">
+    <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Depreciation — tools &amp; repair equipment, Summer 2026</t>
@@ -2632,7 +2632,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="60" outlineLevel="1">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Depreciation — fixtures, Summer 2026</t>
@@ -2642,7 +2642,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="61" outlineLevel="1">
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Depreciation — laptop, Summer 2026</t>
@@ -2652,7 +2652,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="62" outlineLevel="1">
+    <row r="62" collapsed="1">
       <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2665,11 +2665,11 @@
         <v/>
       </c>
     </row>
-    <row r="63" outlineLevel="1">
+    <row r="63">
       <c r="B63" s="3" t="n"/>
       <c r="D63" s="4" t="n"/>
     </row>
-    <row r="64" outlineLevel="1">
+    <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWN</t>
@@ -2678,7 +2678,7 @@
       <c r="C64" s="11" t="n"/>
       <c r="D64" s="11" t="n"/>
     </row>
-    <row r="65" outlineLevel="1">
+    <row r="65" hidden="1" outlineLevel="1">
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Owner's draw — money taken out for personal use</t>
@@ -2688,7 +2688,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="66" outlineLevel="1">
+    <row r="66" collapsed="1">
       <c r="B66" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" t="inlineStr">
         <is>
           <t>Cash — Company received at formation (June 1)</t>
@@ -3299,7 +3299,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="B8" t="inlineStr">
         <is>
           <t>Right of Use — Company received at formation (June 1)</t>
@@ -3309,7 +3309,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" t="inlineStr">
         <is>
           <t>Parts — Company received at formation (June 1)</t>
@@ -3319,7 +3319,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" t="inlineStr">
         <is>
           <t>Tools &amp; Repair Equipment — Company received at formation (June 1)</t>
@@ -3329,7 +3329,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1" outlineLevel="1">
       <c r="B11" t="inlineStr">
         <is>
           <t>Fixtures — Company received at formation (June 1)</t>
@@ -3339,7 +3339,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1" outlineLevel="1">
       <c r="B12" t="inlineStr">
         <is>
           <t>Laptop — Company received at formation (June 1)</t>
@@ -3349,7 +3349,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1" outlineLevel="1">
       <c r="B13" t="inlineStr">
         <is>
           <t>Credit Card — Company assumed the claim at formation (June 1)</t>
@@ -3359,7 +3359,7 @@
         <v>-2030</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1" outlineLevel="1">
       <c r="B14" t="inlineStr">
         <is>
           <t>Customer Deposit — Company assumed the claim at formation (June 1)</t>
@@ -3369,7 +3369,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" collapsed="1">
       <c r="B15" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" t="inlineStr">
         <is>
           <t>Repair collected — Dana R.</t>
@@ -3421,7 +3421,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" hidden="1" outlineLevel="1" ht="16" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
           <t>Parts used — Dana R.</t>
@@ -3431,7 +3431,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" hidden="1" outlineLevel="1" ht="16" customHeight="1">
       <c r="B22" t="inlineStr">
         <is>
           <t>Repair collected — Marcus T.</t>
@@ -3441,7 +3441,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" t="inlineStr">
         <is>
           <t>Repair collected — Priya S.</t>
@@ -3451,7 +3451,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" t="inlineStr">
         <is>
           <t>Parts used — Priya S.</t>
@@ -3461,7 +3461,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" t="inlineStr">
         <is>
           <t>Repair collected — Liam O.</t>
@@ -3471,7 +3471,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" t="inlineStr">
         <is>
           <t>Parts used — Liam O.</t>
@@ -3481,7 +3481,7 @@
         <v>-95</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" t="inlineStr">
         <is>
           <t>Repair collected — Sofia M.</t>
@@ -3491,7 +3491,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" t="inlineStr">
         <is>
           <t>Repair collected — Jamal W.</t>
@@ -3501,7 +3501,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" t="inlineStr">
         <is>
           <t>Parts used — Jamal W.</t>
@@ -3511,7 +3511,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" t="inlineStr">
         <is>
           <t>Repair collected — Erin K.</t>
@@ -3521,7 +3521,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" t="inlineStr">
         <is>
           <t>Parts used — Erin K.</t>
@@ -3531,7 +3531,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" t="inlineStr">
         <is>
           <t>Repair collected — Noah B.</t>
@@ -3541,7 +3541,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" outlineLevel="1">
       <c r="B33" t="inlineStr">
         <is>
           <t>Parts used — Noah B.</t>
@@ -3551,7 +3551,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="1" outlineLevel="1">
       <c r="B34" t="inlineStr">
         <is>
           <t>Rent used — June</t>
@@ -3561,7 +3561,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="1" outlineLevel="1">
       <c r="B35" t="inlineStr">
         <is>
           <t>Rent used — July</t>
@@ -3571,7 +3571,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1" outlineLevel="1">
       <c r="B36" t="inlineStr">
         <is>
           <t>Repair collected — Grace L.</t>
@@ -3581,7 +3581,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" outlineLevel="1">
       <c r="B37" t="inlineStr">
         <is>
           <t>Parts used — Grace L.</t>
@@ -3591,7 +3591,7 @@
         <v>-35</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="1" outlineLevel="1">
       <c r="B38" t="inlineStr">
         <is>
           <t>Repair collected — Theo H.</t>
@@ -3601,7 +3601,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1" outlineLevel="1">
       <c r="B39" t="inlineStr">
         <is>
           <t>Parts used — Theo H.</t>
@@ -3611,7 +3611,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1" outlineLevel="1">
       <c r="B40" t="inlineStr">
         <is>
           <t>Repair collected — Maya P.</t>
@@ -3621,7 +3621,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="1" outlineLevel="1">
       <c r="B41" t="inlineStr">
         <is>
           <t>Parts used — Maya P.</t>
@@ -3631,7 +3631,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1" outlineLevel="1">
       <c r="B42" t="inlineStr">
         <is>
           <t>Repair collected — Owen C.</t>
@@ -3641,7 +3641,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1" outlineLevel="1">
       <c r="B43" t="inlineStr">
         <is>
           <t>Parts used — Owen C.</t>
@@ -3651,7 +3651,7 @@
         <v>-55</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1" outlineLevel="1">
       <c r="B44" t="inlineStr">
         <is>
           <t>Repair collected — Ava D.</t>
@@ -3661,7 +3661,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1" outlineLevel="1">
       <c r="B45" t="inlineStr">
         <is>
           <t>Parts used — Ava D.</t>
@@ -3671,7 +3671,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="1" outlineLevel="1">
       <c r="B46" t="inlineStr">
         <is>
           <t>Repair collected — Leo F.</t>
@@ -3681,7 +3681,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" t="inlineStr">
         <is>
           <t>Parts used — Leo F.</t>
@@ -3691,7 +3691,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" t="inlineStr">
         <is>
           <t>Repair collected — Nina V.</t>
@@ -3701,7 +3701,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="1" outlineLevel="1">
       <c r="B49" t="inlineStr">
         <is>
           <t>Parts used — Nina V.</t>
@@ -3711,7 +3711,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="1" outlineLevel="1">
       <c r="B50" t="inlineStr">
         <is>
           <t>Rent used — August</t>
@@ -3721,7 +3721,7 @@
         <v>-650</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" t="inlineStr">
         <is>
           <t>Repair collected — Caleb G.</t>
@@ -3731,7 +3731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="1" outlineLevel="1">
       <c r="B52" t="inlineStr">
         <is>
           <t>Parts used — Caleb G.</t>
@@ -3741,7 +3741,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" t="inlineStr">
         <is>
           <t>Repair collected — Ruth A.</t>
@@ -3751,7 +3751,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" t="inlineStr">
         <is>
           <t>Parts used — Ruth A.</t>
@@ -3761,7 +3761,7 @@
         <v>-129</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" t="inlineStr">
         <is>
           <t>Repair collected — Sam Q.</t>
@@ -3771,7 +3771,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" t="inlineStr">
         <is>
           <t>Parts used — Sam Q.</t>
@@ -3781,7 +3781,7 @@
         <v>-70</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" t="inlineStr">
         <is>
           <t>Repair collected — Westville Bike Share</t>
@@ -3791,7 +3791,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" t="inlineStr">
         <is>
           <t>Parts used — Westville Bike Share</t>
@@ -3801,7 +3801,7 @@
         <v>-105</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" t="inlineStr">
         <is>
           <t>Repair delivered — Ridgeline Trail Crew, billed net 15 (unpaid)</t>
@@ -3811,7 +3811,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" t="inlineStr">
         <is>
           <t>Parts used — Ridgeline Trail Crew</t>
@@ -3821,7 +3821,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" t="inlineStr">
         <is>
           <t>Frame delivered — J. Smith (deposit earned)</t>
@@ -3831,7 +3831,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="1" outlineLevel="1">
       <c r="B62" t="inlineStr">
         <is>
           <t>Parts used — J. Smith</t>
@@ -3841,7 +3841,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" outlineLevel="1">
       <c r="B63" t="inlineStr">
         <is>
           <t>Depreciation — tools &amp; repair equipment, Summer 2026</t>
@@ -3851,7 +3851,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="1" outlineLevel="1">
       <c r="B64" t="inlineStr">
         <is>
           <t>Depreciation — fixtures, Summer 2026</t>
@@ -3861,7 +3861,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="1" outlineLevel="1">
       <c r="B65" t="inlineStr">
         <is>
           <t>Depreciation — laptop, Summer 2026</t>
@@ -3871,7 +3871,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" collapsed="1">
       <c r="B66" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1" outlineLevel="1">
       <c r="B69" t="inlineStr">
         <is>
           <t>Owner's draw — money taken out for personal use</t>
@@ -3901,7 +3901,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" collapsed="1">
       <c r="B70" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D132"/>
+  <dimension ref="B1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -563,170 +563,171 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Rent paid in advance (the lease)</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Park Tool repair stand</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Smith's deposit received</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" hidden="1" outlineLevel="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Covered from your personal funds</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Deposited to open the LLC bank account</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
         <v>1300</v>
       </c>
     </row>
-    <row r="15" collapsed="1">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUM(D3:D14)</f>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
         <v>1300</v>
         <v/>
       </c>
     </row>
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Dana R.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Marcus T.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Priya S.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Liam O.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Sofia M.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Erin K.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Noah B.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Grace L.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Theo H.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Maya P.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
     <row r="16" hidden="1" outlineLevel="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Dana R.</t>
+          <t>Repair collected — Owen C.</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" hidden="1" outlineLevel="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Marcus T.</t>
+          <t>Repair collected — Ava D.</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" hidden="1" outlineLevel="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Priya S.</t>
+          <t>Repair collected — Leo F.</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Liam O.</t>
+          <t>Repair collected — Nina V.</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -736,396 +737,416 @@
     <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Sofia M.</t>
+          <t>Repair collected — Caleb G.</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Jamal W.</t>
+          <t>Repair collected — Ruth A.</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>360</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Erin K.</t>
+          <t>Repair collected — Sam Q.</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>225</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Noah B.</t>
+          <t>Repair collected — Westville Bike Share</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Grace L.</t>
+          <t>Parts bought — June</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>240</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Theo H.</t>
+          <t>Parts bought — July</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>240</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Maya P.</t>
+          <t>Parts bought — August</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>450</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Owen C.</t>
+          <t>Rent paid — June</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>360</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ava D.</t>
+          <t>Rent paid — July</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>270</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Leo F.</t>
+          <t>Rent paid — August</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>240</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Nina V.</t>
+          <t>New repair tool</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>300</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Caleb G.</t>
+          <t>Credit card paid off</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>240</v>
+        <v>-2030</v>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ruth A.</t>
+          <t>Money taken out for personal use</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="33" hidden="1" outlineLevel="1">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Westville Bike Share</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — June</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — July</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="37" hidden="1" outlineLevel="1">
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — August</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="38" hidden="1" outlineLevel="1">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — June</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — July</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="1">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — August</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="41" hidden="1" outlineLevel="1">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>New repair tool</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="42" hidden="1" outlineLevel="1">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Credit card paid off</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-2030</v>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Money taken out for personal use</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
         <v>-600</v>
       </c>
     </row>
-    <row r="44" collapsed="1">
-      <c r="B44" s="16" t="inlineStr">
+    <row r="33" collapsed="1">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="13">
-        <f>D15+SUM(D16:D43)</f>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="13">
+        <f>D4+SUM(D5:D32)</f>
         <v>620</v>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="7" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+    </row>
+    <row r="36" hidden="1" outlineLevel="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Ridgeline Trail Crew — finished Aug 28, net 15 (unpaid)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" collapsed="1">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="13">
+        <f>SUM(D36:D36)</f>
+        <v>300</v>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="n"/>
+      <c r="D38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Right of Use</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+    </row>
+    <row r="40" hidden="1" outlineLevel="1">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="41" collapsed="1">
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="13">
+        <f>SUM(D40:D40)</f>
+        <v>650</v>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="13">
+        <f>D41</f>
+        <v>650</v>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="n"/>
+      <c r="D43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" collapsed="1">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="13">
+        <f>SUM(D45:D45)</f>
+        <v>200</v>
+        <v/>
+      </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Ridgeline Trail Crew — finished Aug 28, net 15 (unpaid)</t>
+          <t>Chains ×10 (June)</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" collapsed="1">
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>11-spd cassettes ×4 (June)</t>
         </is>
       </c>
       <c r="C48" s="17" t="n"/>
-      <c r="D48" s="13">
-        <f>SUM(D47:D47)</f>
-        <v>300</v>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Right of Use</t>
+      <c r="D48" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Brake pad sets ×12 (June)</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Cables + housing (assorted) (June)</t>
         </is>
       </c>
       <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
+      <c r="D50" s="4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="51" hidden="1" outlineLevel="1">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Last month's rent, paid in advance (on deposit)</t>
+          <t>Tubes ×10 (June)</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="52" collapsed="1">
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Chainrings + jockey wheels (July)</t>
         </is>
       </c>
       <c r="C52" s="17" t="n"/>
-      <c r="D52" s="13">
-        <f>SUM(D51:D51)</f>
-        <v>650</v>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
+      <c r="D52" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="1">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Bottom brackets ×3 (July)</t>
         </is>
       </c>
       <c r="C53" s="17" t="n"/>
-      <c r="D53" s="13">
-        <f>D52</f>
-        <v>650</v>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Parts</t>
+      <c r="D53" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Shift cables + housing (July)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="1">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Tubeless sealant + valves (July)</t>
         </is>
       </c>
       <c r="C55" s="11" t="n"/>
-      <c r="D55" s="11" t="n"/>
+      <c r="D55" s="4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Chains</t>
+          <t>Spokes + nipples (July)</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Brake pads</t>
+          <t>Tires ×4 (August)</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Derailleur cables</t>
+          <t>Brake pads (assorted) (August)</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Cables + housing (August)</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Bottom brackets</t>
+          <t>Tubes ×8 (August)</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" hidden="1" outlineLevel="1">
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Spokes</t>
+          <t>Small parts (bolts, tape) (August)</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
@@ -1135,700 +1156,390 @@
     <row r="62" hidden="1" outlineLevel="1">
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Tubes</t>
+          <t>Parts used — Dana R.</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" collapsed="1">
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Priya S.</t>
         </is>
       </c>
       <c r="C63" s="17" t="n"/>
-      <c r="D63" s="13">
-        <f>SUM(D56:D62)</f>
+      <c r="D63" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Liam O.</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Erin K.</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Noah B.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Grace L.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Theo H.</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Maya P.</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Owen C.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ava D.</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Leo F.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Nina V.</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Caleb G.</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ruth A.</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>-129</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Sam Q.</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Westville Bike Share</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ridgeline Trail Crew</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — J. Smith</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="81" collapsed="1">
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="13">
+        <f>D46+SUM(D47:D80)</f>
         <v>200</v>
         <v/>
       </c>
     </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Chains ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>11-spd cassettes ×4 (June)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Brake pad sets ×12 (June)</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (assorted) (June)</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Chainrings + jockey wheels (July)</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Bottom brackets ×3 (July)</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="71" hidden="1" outlineLevel="1">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Shift cables + housing (July)</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" hidden="1" outlineLevel="1">
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Tubeless sealant + valves (July)</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Spokes + nipples (July)</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" hidden="1" outlineLevel="1">
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Tires ×4 (August)</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Brake pads (assorted) (August)</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="76" hidden="1" outlineLevel="1">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (August)</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="77" hidden="1" outlineLevel="1">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×8 (August)</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Small parts (bolts, tape) (August)</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Dana R.</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Priya S.</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="81" hidden="1" outlineLevel="1">
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Liam O.</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>-95</v>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Jamal W.</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="83" hidden="1" outlineLevel="1">
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Erin K.</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>-40</v>
-      </c>
+    <row r="82">
+      <c r="B82" s="3" t="n"/>
+      <c r="D82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Tools &amp; Repair Equipment</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
     </row>
     <row r="84" hidden="1" outlineLevel="1">
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Noah B.</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="85" hidden="1" outlineLevel="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Grace L.</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>-35</v>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="85" collapsed="1">
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="13">
+        <f>SUM(D84:D84)</f>
+        <v>1200</v>
+        <v/>
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Theo H.</t>
+          <t>New repair tool bought this season</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-25</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="1">
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Maya P.</t>
+          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>-125</v>
-      </c>
-    </row>
-    <row r="88" hidden="1" outlineLevel="1">
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Owen C.</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>-55</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" outlineLevel="1">
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ava D.</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="90" hidden="1" outlineLevel="1">
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Leo F.</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>-100</v>
-      </c>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="88" collapsed="1">
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="13">
+        <f>D85+SUM(D86:D87)</f>
+        <v>1440</v>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="3" t="n"/>
+      <c r="D89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="11" t="n"/>
     </row>
     <row r="91" hidden="1" outlineLevel="1">
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Nina V.</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="92" hidden="1" outlineLevel="1">
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Caleb G.</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>-25</v>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="92" collapsed="1">
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="13">
+        <f>SUM(D91:D91)</f>
+        <v>750</v>
+        <v/>
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Ruth A.</t>
+          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>-129</v>
-      </c>
-    </row>
-    <row r="94" hidden="1" outlineLevel="1">
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="95" hidden="1" outlineLevel="1">
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Westville Bike Share</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="96" hidden="1" outlineLevel="1">
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ridgeline Trail Crew</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>-75</v>
-      </c>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="94" collapsed="1">
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="13">
+        <f>D92+SUM(D93:D93)</f>
+        <v>710</v>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="3" t="n"/>
+      <c r="D95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
     </row>
     <row r="97" hidden="1" outlineLevel="1">
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Parts used — J. Smith</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>-36</v>
+        <v>610</v>
       </c>
     </row>
     <row r="98" collapsed="1">
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2026</t>
+          <t>Balance, June 1, 2026</t>
         </is>
       </c>
       <c r="C98" s="17" t="n"/>
       <c r="D98" s="13">
-        <f>D63+SUM(D64:D97)</f>
-        <v>200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Tools &amp; Repair Equipment</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="n"/>
-      <c r="D100" s="11" t="n"/>
-    </row>
-    <row r="101" hidden="1" outlineLevel="1">
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Repair stand</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" hidden="1" outlineLevel="1">
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Air compressor</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="103" hidden="1" outlineLevel="1">
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Parts washer</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="104" hidden="1" outlineLevel="1">
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="105" hidden="1" outlineLevel="1">
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Cone wrench set</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="106" hidden="1" outlineLevel="1">
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Torque wrench</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="107" hidden="1" outlineLevel="1">
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Hex/Allen set</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="108" hidden="1" outlineLevel="1">
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Cable cutters</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="109" hidden="1" outlineLevel="1">
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Chain breaker</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" hidden="1" outlineLevel="1">
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Tire levers</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" hidden="1" outlineLevel="1">
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Bench grinder</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="112" hidden="1" outlineLevel="1">
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Headset press</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" hidden="1" outlineLevel="1">
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Shop vacuum</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" collapsed="1">
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C114" s="17" t="n"/>
-      <c r="D114" s="13">
-        <f>SUM(D101:D113)</f>
-        <v>1200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="115" hidden="1" outlineLevel="1">
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>New repair tool bought this season</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="116" hidden="1" outlineLevel="1">
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="117" collapsed="1">
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C117" s="17" t="n"/>
-      <c r="D117" s="13">
-        <f>D114+SUM(D115:D116)</f>
-        <v>1440</v>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="n"/>
-      <c r="D119" s="11" t="n"/>
-    </row>
-    <row r="120" hidden="1" outlineLevel="1">
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Desk</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="121" hidden="1" outlineLevel="1">
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Shelving units</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="122" hidden="1" outlineLevel="1">
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Display rack</t>
-        </is>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="123" hidden="1" outlineLevel="1">
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Pegboard + hooks</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="124" collapsed="1">
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="13">
-        <f>SUM(D120:D123)</f>
-        <v>750</v>
-        <v/>
-      </c>
-    </row>
-    <row r="125" hidden="1" outlineLevel="1">
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="126" collapsed="1">
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="13">
-        <f>D124+SUM(D125:D125)</f>
-        <v>710</v>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C128" s="11" t="n"/>
-      <c r="D128" s="11" t="n"/>
-    </row>
-    <row r="129" hidden="1" outlineLevel="1">
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Laptop (from home)</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="130" collapsed="1">
-      <c r="B130" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="n"/>
-      <c r="D130" s="13">
-        <f>SUM(D129:D129)</f>
+        <f>SUM(D97:D97)</f>
         <v>610</v>
         <v/>
       </c>
     </row>
-    <row r="131" hidden="1" outlineLevel="1">
-      <c r="B131" s="3" t="inlineStr">
+    <row r="99" hidden="1" outlineLevel="1">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>Depreciation — Summer 2026 (the season's share of the cost)</t>
         </is>
       </c>
-      <c r="D131" s="4" t="n">
+      <c r="D99" s="4" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="132" collapsed="1">
-      <c r="B132" s="16" t="inlineStr">
+    <row r="100" collapsed="1">
+      <c r="B100" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C132" s="17" t="n"/>
-      <c r="D132" s="13">
-        <f>D130+SUM(D131:D131)</f>
+      <c r="C100" s="17" t="n"/>
+      <c r="D100" s="13">
+        <f>D98+SUM(D99:D99)</f>
         <v>580</v>
         <v/>
       </c>
@@ -1845,7 +1556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D17"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1870,153 +1581,109 @@
       <c r="C2" s="11" t="n"/>
       <c r="D2" s="11" t="n"/>
     </row>
-    <row r="3" outlineLevel="1">
+    <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Charged — hand tools</t>
+          <t>Company assumed the claim at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Charged — air compressor</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" outlineLevel="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Charged — parts washer</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Charged — wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Charged — fixtures</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="8" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Charged — parts (QBP order)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="inlineStr">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="13">
-        <f>SUM(D3:D8)</f>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
         <v>2030</v>
         <v/>
       </c>
     </row>
-    <row r="10" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Paid off in full this season</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>-2030</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+    <row r="6" collapsed="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="13">
-        <f>D9+SUM(D10:D10)</f>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="13">
+        <f>D4+SUM(D5:D5)</f>
         <v>0</v>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Customer Deposit</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Smith's advance for a custom frame</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Company assumed the claim at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="10" collapsed="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUM(D14:D14)</f>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="13">
+        <f>SUM(D9:D9)</f>
         <v>220</v>
         <v/>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Built and delivered Smith's frame — no longer owed</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="4" t="n">
         <v>-220</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+    <row r="12" collapsed="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="13">
-        <f>D15+SUM(D16:D16)</f>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="13">
+        <f>D10+SUM(D11:D11)</f>
         <v>0</v>
         <v/>
       </c>
@@ -3280,8 +2947,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -3393,7 +3058,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
@@ -3883,7 +3547,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
@@ -881,7 +881,7 @@
       <c r="B34" s="7" t="n"/>
       <c r="D34" s="4" t="n"/>
     </row>
-    <row r="35" hidden="1" outlineLevel="1">
+    <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
@@ -890,7 +890,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
     </row>
-    <row r="36" hidden="1" outlineLevel="1">
+    <row r="36" outlineLevel="1">
       <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Ridgeline Trail Crew — finished Aug 28, net 15 (unpaid)</t>
@@ -900,7 +900,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" collapsed="1">
+    <row r="37">
       <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-4-1.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D100"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Company received at formation (June 1)</t>
+          <t>additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -580,7 +580,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>1300</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -837,7 +836,7 @@
     <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>New repair tool</t>
+          <t>Wheel truing stand</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
@@ -874,7 +873,6 @@
       <c r="D33" s="13">
         <f>D4+SUM(D5:D32)</f>
         <v>620</v>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -910,7 +908,6 @@
       <c r="D37" s="13">
         <f>SUM(D36:D36)</f>
         <v>300</v>
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -946,7 +943,6 @@
       <c r="D41" s="13">
         <f>SUM(D40:D40)</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="42">
@@ -959,7 +955,6 @@
       <c r="D42" s="13">
         <f>D41</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -995,7 +990,6 @@
       <c r="D46" s="13">
         <f>SUM(D45:D45)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
@@ -1354,7 +1348,6 @@
       <c r="D81" s="13">
         <f>D46+SUM(D47:D80)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="82">
@@ -1390,13 +1383,12 @@
       <c r="D85" s="13">
         <f>SUM(D84:D84)</f>
         <v>1200</v>
-        <v/>
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>New repair tool bought this season</t>
+          <t>Wheel truing stand bought this season</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
@@ -1423,7 +1415,6 @@
       <c r="D88" s="13">
         <f>D85+SUM(D86:D87)</f>
         <v>1440</v>
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -1459,7 +1450,6 @@
       <c r="D92" s="13">
         <f>SUM(D91:D91)</f>
         <v>750</v>
-        <v/>
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="1">
@@ -1482,7 +1472,6 @@
       <c r="D94" s="13">
         <f>D92+SUM(D93:D93)</f>
         <v>710</v>
-        <v/>
       </c>
     </row>
     <row r="95">
@@ -1518,7 +1507,6 @@
       <c r="D98" s="13">
         <f>SUM(D97:D97)</f>
         <v>610</v>
-        <v/>
       </c>
     </row>
     <row r="99" hidden="1" outlineLevel="1">
@@ -1541,7 +1529,6 @@
       <c r="D100" s="13">
         <f>D98+SUM(D99:D99)</f>
         <v>580</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1601,7 +1588,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>2030</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -1624,7 +1610,6 @@
       <c r="D6" s="13">
         <f>D4+SUM(D5:D5)</f>
         <v>0</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1661,7 +1646,6 @@
       <c r="D10" s="13">
         <f>SUM(D9:D9)</f>
         <v>220</v>
-        <v/>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -1685,7 +1669,6 @@
       <c r="D12" s="13">
         <f>D10+SUM(D11:D11)</f>
         <v>0</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1728,7 +1711,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cash — Company received at formation (June 1)</t>
+          <t>Cash — additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -1818,7 +1801,6 @@
       <c r="D11" s="13">
         <f>SUM(D3:D10)</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1831,7 +1813,6 @@
       <c r="D12" s="13">
         <f>D11</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2310,6 @@
       <c r="D62" s="13">
         <f>D15+SUM(D16:D61)</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -2365,7 +2345,6 @@
       <c r="D66" s="13">
         <f>SUM(D65:D65)</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
     <row r="70" outlineLevel="1"/>
@@ -2381,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2650,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D46"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="3.1640625" customWidth="1" min="1" max="1"/>
@@ -2714,9 +2693,9 @@
       <c r="D7" s="25">
         <f>D6</f>
         <v>6020</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="27" t="inlineStr">
         <is>
@@ -2766,9 +2745,9 @@
       <c r="D13" s="25">
         <f>SUM(D10:D12)</f>
         <v>3380</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -2779,7 +2758,6 @@
       <c r="D15" s="25">
         <f>D7-D13</f>
         <v>2640</v>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -2918,7 +2896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D70"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="3.33203125" customWidth="1" min="1" max="1"/>
@@ -2947,6 +2925,8 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -2957,7 +2937,7 @@
     <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cash — Company received at formation (June 1)</t>
+          <t>Cash — additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3043,7 +3023,6 @@
       <c r="D15">
         <f>SUM(D7:D14)</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -3055,9 +3034,9 @@
       <c r="D16">
         <f>D15</f>
         <v>2460</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
@@ -3544,9 +3523,9 @@
       <c r="D66">
         <f>D19+SUM(D20:D65)</f>
         <v>2640</v>
-        <v/>
-      </c>
-    </row>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
@@ -3573,7 +3552,6 @@
       <c r="D70">
         <f>SUM(D69:D69)</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
   </sheetData>
